--- a/output/2026-09-01_11_Italia_Liguria_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-01_11_Italia_Liguria_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Forniture navali e industriali dal 1878; utensili manuali/elettrici, cuscinetti, utensili da taglio. Verificato su Pagine Bianche e sito ufficiale.</t>
+          <t>Forniture navali e industriali dal 1878; utensili manuali/elettrici, cuscinetti, utensili da taglio. Verificato su Pagine Bianche e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -647,7 +647,6 @@
           <t>Falzoni &amp; Parodi S.n.c.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Genova (GE), Liguria</t>
@@ -663,7 +662,6 @@
           <t>010 6982681 / 010 6982734</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Commercio ingrosso utensili e lame industriali (lame da sega). P.IVA 01124340108 confermata su registri camerali. Nessun sito/email pubblici trovati.</t>
@@ -708,7 +706,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Produttore/distributore di utensili da taglio, maschi, filiere e frese, spin-off ex reparto utensili Ansaldo. Verificato su più fonti.</t>
+          <t>Produttore/distributore di utensili da taglio, maschi, filiere e frese, spin-off ex reparto utensili Ansaldo. Verificato su più fonti. [DUPLICATO — vedi anche: 2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -743,7 +741,6 @@
           <t>010 580620 / 010 581422 / 010 592857</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Fondata nel 1940, utensileria, elettroutensili, cuscinetti, paranchi, compressori, antinfortunistica.</t>
@@ -781,10 +778,9 @@
           <t>010 6592011</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Distributore tecnico-industriale attivo da oltre 40 anni (cuscinetti, utensili per meccanica generale/precisione, strumentazione), 5 sedi in Nord Italia.</t>
+          <t>Distributore tecnico-industriale attivo da oltre 40 anni (cuscinetti, utensili per meccanica generale/precisione, strumentazione), 5 sedi in Nord Italia. [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -819,10 +815,9 @@
           <t>0187 982128</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Filiale spezzina della stessa società Bi.Erre.Di S.p.A. (sede legale Genova); mantenuta come voce separata per copertura territoriale SP.</t>
+          <t>Filiale spezzina della stessa società Bi.Erre.Di S.p.A. (sede legale Genova); mantenuta come voce separata per copertura territoriale SP. [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -906,7 +901,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Partner Metabo LiHD e Spit; forniture tecniche industriali, elettroutensili, cuscinetti. Indirizzo esatto: Fraz. Lidora 49E, 17017 Cosseria (SV).</t>
+          <t>Partner Metabo LiHD e Spit; forniture tecniche industriali, elettroutensili, cuscinetti. Indirizzo esatto: Fraz. Lidora 49E, 17017 Cosseria (SV). [DUPLICATO — vedi anche: 2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -948,7 +943,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ferramenta/bulloneria storica dal 1890, Piazza Giulio II. Email fornita non riscontrata direttamente nelle fonti pubbliche (che riportano invece fava.francesco@fastwebnet.it).</t>
+          <t>Ferramenta/bulloneria storica dal 1890, Piazza Giulio II. Email fornita non riscontrata direttamente nelle fonti pubbliche (che riportano invece fava.francesco@fastwebnet.it). [DUPLICATO — vedi anche: 2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -983,7 +978,6 @@
           <t>019 860455</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Materiali edili, ferramenta, macchinari e utensili edili, attiva dal 1877. Prevalentemente edilizia: categoria di confine rispetto a metalworking puro.</t>
@@ -1028,7 +1022,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ingrosso/dettaglio utensileria industriale (chiavi, frese, punte, maschiatrici, filettatrici), macchine e generatori. 1500 mq tra magazzino e uffici.</t>
+          <t>Ingrosso/dettaglio utensileria industriale (chiavi, frese, punte, maschiatrici, filettatrici), macchine e generatori. 1500 mq tra magazzino e uffici. [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1085,7 +1079,6 @@
           <t>100x100 Di Riccardo Sommovigo</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>La Spezia (SP), Liguria</t>
@@ -1096,7 +1089,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>riccardosommovigo@libero.it</t>
@@ -1146,7 +1138,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dal 1963, vendita utensili professionali manuali/elettrici/a batteria (Bosch, DeWalt, Makita), antinfortunistica, antincendio.</t>
+          <t>Dal 1963, vendita utensili professionali manuali/elettrici/a batteria (Bosch, DeWalt, Makita), antinfortunistica, antincendio. [DUPLICATO — vedi anche: 2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1161,7 +1153,6 @@
           <t>Ferrotek S.n.c. di Bottaro Marco ed Elisa</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Imperia (IM), Liguria</t>
@@ -1219,7 +1210,6 @@
           <t>0183 493176</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Utensileria, ferramenta, attrezzature da lavoro; rivenditore autorizzato Milwaukee, AEG, Cofra.</t>
@@ -1279,7 +1269,6 @@
           <t>Euroutensili Service di Ori Adelio</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Imperia (IM), Liguria</t>
@@ -1290,11 +1279,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ferramenta-utensileria confermata su directory (Pagine Gialle) all'indirizzo Via Cornelio Tacito 2, Ventimiglia (IM).</t>
+          <t>Ferramenta-utensileria confermata su directory (Pagine Gialle) all'indirizzo Via Cornelio Tacito 2, Ventimiglia (IM). [DUPLICATO — vedi anche: 2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
